--- a/output/港大经管上海中心_前期费用与交付清单.xlsx
+++ b/output/港大经管上海中心_前期费用与交付清单.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03-首场执行" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04-双方分工" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05-付款与开票" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06-对方需求摘录" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'00-封面'!$1:$4</definedName>
@@ -21,6 +22,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'03-首场执行'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'04-双方分工'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'05-付款与开票'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'06-对方需求摘录'!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -606,14 +608,14 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>外滩·产业课堂  前期费用与交付清单</t>
+          <t>外滩·出海课堂  前期费用与交付清单</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>香港大学经管学院上海中心  ×  复旦大学住房政策研究中心、上海市杨浦区科技企业联合会    V1.0 建议稿  2026年9月</t>
+          <t>香港大学经管学院上海中心  ×  复旦大学住房政策研究中心、上海市杨浦区科技企业联合会    V1.1 建议稿  2026年9月    依据2026年9月3日交流</t>
         </is>
       </c>
     </row>
@@ -637,7 +639,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>外滩·产业课堂</t>
+          <t>外滩·出海课堂</t>
         </is>
       </c>
       <c r="C5" s="6" t="n"/>
@@ -665,7 +667,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>潘嘉琰  招生官（华东 · EMBA）</t>
+          <t>潘嘉琰  华东华中 EMBA 招生与市场（经管上海中心平台）</t>
         </is>
       </c>
       <c r="C7" s="6" t="n"/>
@@ -791,7 +793,7 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>只收前期费用，不碰学费分成，不承诺录取人数</t>
+          <t>只收前期费用；主赛道出海；不碰学费分成；不承诺录取人数</t>
         </is>
       </c>
       <c r="C16" s="6" t="n"/>
@@ -800,7 +802,7 @@
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>不把外滩中心做成宣讲会会场，而做成可持续出 EMBA 生源的产业课堂：港大讲全球视野与学位通道，我方送进对的产业高管；先收一笔前期策划费，把 90 天和首场锁住。</t>
+          <t>出海是港大点名的合作赛道。先让上海中心主任到高质量的场有直观感受，再把外滩课堂做成 EMBA 粘性；先收一笔前期策划费，90 天把这两件事锁住。</t>
         </is>
       </c>
     </row>
@@ -827,7 +829,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L外滩·产业课堂</oddHeader>
+    <oddHeader>&amp;L外滩·出海课堂</oddHeader>
     <oddFooter>&amp;R第 &amp;P 页 / 共 &amp;N 页</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -843,7 +845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -862,7 +864,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>对外只报一个数：88,000 元。下表用于内部对齐成本与对甲方说明覆盖范围。</t>
+          <t>对外只报一个数：88,000 元。含外滩出海首场 + 一次主任体验组织。</t>
         </is>
       </c>
     </row>
@@ -894,11 +896,11 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>90天联合策划</t>
+          <t>90天出海联合策划</t>
         </is>
       </c>
       <c r="C5" s="13" t="n">
-        <v>28000</v>
+        <v>24000</v>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
@@ -916,7 +918,7 @@
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>18000</v>
+        <v>16000</v>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
@@ -930,15 +932,15 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>首场闭门课执行</t>
+          <t>首场出海闭门课</t>
         </is>
       </c>
       <c r="C7" s="13" t="n">
-        <v>32000</v>
+        <v>28000</v>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>外滩现场统筹、物料、签到、主持配合（规模 30–40 人）</t>
+          <t>外滩现场统筹、物料、签到（规模 30–40 人）</t>
         </is>
       </c>
     </row>
@@ -948,7 +950,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>会后纪要与分级</t>
+          <t>主任体验场组织</t>
         </is>
       </c>
       <c r="C8" s="14" t="n">
@@ -956,53 +958,59 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
+          <t>借我方高规格出海场邀主任到场，不另向对方加收</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>会后纪要与分级</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
           <t>7日内纪要、A/B/C名单、协助预约面试窗口</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr"/>
-      <c r="B9" s="3" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr"/>
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>合计（前期费用）</t>
         </is>
       </c>
-      <c r="C9" s="15">
-        <f>SUM(C5:C8)</f>
+      <c r="C10" s="15">
+        <f>SUM(C5:C9)</f>
         <v/>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>一次性支付，包干，不含协议外增项</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>不包含</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>学费、报名费、留位费及任何按人头的招生分成（本协议不做）</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="n"/>
-      <c r="D12" s="11" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>第二场及以后场次（建议 68,000 元/场，另签确认单）</t>
+          <t>学费、报名费、留位费及任何按人头的招生分成（本协议不做）</t>
         </is>
       </c>
       <c r="C13" s="11" t="n"/>
@@ -1010,11 +1018,11 @@
     </row>
     <row r="14">
       <c r="A14" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>差旅、礼品、嘉宾课酬、媒体投放等协议外增项（事前书面确认）</t>
+          <t>第二场及以后场次（建议 68,000 元/场，另签确认单）</t>
         </is>
       </c>
       <c r="C14" s="11" t="n"/>
@@ -1022,38 +1030,50 @@
     </row>
     <row r="15">
       <c r="A15" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>港大侧录取、面试、学位授予等学院内部职权</t>
+          <t>本部企业出海高级管理课程的联合招生与分成（可另议推广，资料由对方提供）</t>
         </is>
       </c>
       <c r="C15" s="11" t="n"/>
       <c r="D15" s="11" t="n"/>
     </row>
-    <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>原创谷日常运营、股权投资，以及灰色跨境结算等非正式议题（对外一律不采用）</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="n"/>
+      <c r="D16" s="11" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>后续场次（不自动生效）</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>第二场及以后</t>
         </is>
       </c>
-      <c r="C18" s="19" t="n">
+      <c r="C19" s="19" t="n">
         <v>68000</v>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>另签确认单，含执行不含新一轮 90 天策划</t>
         </is>
@@ -1062,18 +1082,18 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A18:D18"/>
     <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L外滩·产业课堂</oddHeader>
+    <oddHeader>&amp;L外滩·出海课堂</oddHeader>
     <oddFooter>&amp;R第 &amp;P 页 / 共 &amp;N 页</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -1089,7 +1109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1142,17 +1162,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>签约与到账</t>
+          <t>签约与资料</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>签署页信息齐套；前期费用到账；首场主题/日期/档期确认单</t>
+          <t>签署齐套、费用到账、出海课资料、主任窗口与首场档期</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>银行回单 + 确认邮件</t>
+          <t>银行回单 + 邮件</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1189,7 @@
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>客群画像 1 份、邀约话术 1 份、定向名单 ≥80 人初稿</t>
+          <t>出海客群画像、邀约话术、定向名单 ≥80 人初稿</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -1186,12 +1206,12 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>首场执行</t>
+          <t>外滩首场</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>现场执行、签到表、议程、影像（如允许）</t>
+          <t>出海闭门课现场、签到表、议程</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -1208,72 +1228,80 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>会后 7 日</t>
+          <t>主任体验</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>纪要、A/B/C 分级名单、面试窗口协助记录</t>
+          <t>高规格出海场书面邀约（出席以其公务为准）</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>邮件提交</t>
+          <t>书面邀约 + 活动举办</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
+          <t>D22–D45</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>会后 7 日</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>纪要、A/B/C 分级名单、面试窗口协助记录</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>邮件提交</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
           <t>D46–D90</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>固化复制</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>首场复盘 1 份、后两场议题日历（不含第二场执行）</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>备忘</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>复盘；出海课联合推广备忘；原创谷/海外模块清单（不验收）</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>邮件提交</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>工作目标（非违约条款）</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>到场</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>30–40 人，签到率 ≥ 70%（以确认出席名单计）</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="n"/>
-      <c r="D12" s="11" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>画像匹配</t>
+          <t>到场</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>到场者中符合 EMBA 经验门槛的比例 ≥ 60%</t>
+          <t>30–40 人，签到率 ≥ 70%（以确认出席名单计）</t>
         </is>
       </c>
       <c r="C13" s="11" t="n"/>
@@ -1282,12 +1310,12 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>会后 7 日</t>
+          <t>画像匹配</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>A/B 类意向合计不少于 8 人，完整纪要与共管名单</t>
+          <t>到场者中符合 EMBA 经验门槛或明确出海决策权的比例 ≥ 60%</t>
         </is>
       </c>
       <c r="C14" s="11" t="n"/>
@@ -1296,31 +1324,45 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>不承诺</t>
+          <t>会后 7 日</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>不承诺录取人数、不承诺学费流水——录取权在学院</t>
+          <t>A/B 类意向合计不少于 8 人，完整纪要与共管名单</t>
         </is>
       </c>
       <c r="C15" s="11" t="n"/>
       <c r="D15" s="11" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>主任体验</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>90 天内完成一次正式邀约；是否出席以其公务为准，不构成强制</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="n"/>
+      <c r="D16" s="11" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L外滩·产业课堂</oddHeader>
+    <oddHeader>&amp;L外滩·出海课堂</oddHeader>
     <oddFooter>&amp;R第 &amp;P 页 / 共 &amp;N 页</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -1355,7 +1397,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>产业决策者的全球能力：AI、跨境与城市机会</t>
+          <t>企业出海的港大路径：港股、跨境与产业决策</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1431,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>产业决策者的全球能力：AI、跨境与城市机会</t>
+          <t>企业出海的港大路径：港股、跨境与产业决策</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -1455,7 +1497,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>科企联会员企业主/高管为主，辅以不动产与硬科技决策者</t>
+          <t>有出海或港股意向的企业主/高管，辅以科企联与产业决策者</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
@@ -1506,7 +1548,7 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>签到、合影、中心空间简介</t>
+          <t>签到、合影、中心与百年校庆墙简介</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr"/>
@@ -1524,7 +1566,7 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>港大经管：学位通道与华东布局（招生官主持）</t>
+          <t>港大经管：出海优势与华东布局（招生官主持）</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr"/>
@@ -1542,7 +1584,7 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>主题分享（港大师资或杰出校友，院方指定）</t>
+          <t>主题分享（港大师资或校友，院方指定，聚焦出海/港股）</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr"/>
@@ -1638,7 +1680,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L外滩·产业课堂</oddHeader>
+    <oddHeader>&amp;L外滩·出海课堂</oddHeader>
     <oddFooter>&amp;R第 &amp;P 页 / 共 &amp;N 页</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -1729,7 +1771,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>指定师资/校友嘉宾，安排招生官现场主持与一对一</t>
+          <t>指定师资/校友嘉宾；潘老师现场主持与一对一</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
@@ -1751,7 +1793,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>负责面试、录取、学位等学院内部流程</t>
+          <t>协助邀请中心主任出席一次甲方高规格出海活动</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -1773,7 +1815,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>指定唯一接口人（建议：潘嘉琰）</t>
+          <t>面试、录取、学位等学院内部流程；发出海课介绍资料</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
@@ -1795,7 +1837,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>90 天策划、议题设计、邀约执行与现场统筹</t>
+          <t>90 天出海策划、议题、邀约与外滩首场统筹</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -1839,7 +1881,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>会后纪要、意向分级、协助预约面试窗口</t>
+          <t>组织一次可供主任体验的高规格出海活动现场</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -1861,7 +1903,7 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>指定运营结算主体开票、收款、对账</t>
+          <t>会后纪要、意向分级；指定结算主体开票收款</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -1883,7 +1925,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L外滩·产业课堂</oddHeader>
+    <oddHeader>&amp;L外滩·出海课堂</oddHeader>
     <oddFooter>&amp;R第 &amp;P 页 / 共 &amp;N 页</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -2190,7 +2232,252 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L外滩·产业课堂</oddHeader>
+    <oddHeader>&amp;L外滩·出海课堂</oddHeader>
+    <oddFooter>&amp;R第 &amp;P 页 / 共 &amp;N 页</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>对方需求摘录（2026年9月3日 外滩中心交流）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>整理自洽谈记录。对外方案采用出海、经管学院层级、主任体验；不采用闲聊中的非正式跨境口径。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>要点</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>本期如何用</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>听懂</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>合作层级</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>从上海中心角度看，不能只停在 EMBA，要从经管学院维度做。</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>协议第一条分层</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>听懂</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>主赛道</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>国内 AI 港大并无断崖优势；出海、港股、跨境金融才是港大打不输的牌。</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>首场与方案主赛道</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>听懂</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>怎么启动</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>有总领事、高质量企业家在场的活动，潘老师邀中心主任到场，让主任先有感受。</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>主任体验含在前期费</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>听懂</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>角色</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>潘老师是 EMBA 粘性，管华东华中招生与市场；多维度合作在主任，不在招生官越权承诺。</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>接口人权限边界</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>需求</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>高端教育招生</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>华东华中 EMBA / 高端项目要做起来。对方称今年已超北京、深圳中心，要持续高质量到场，而不是一次性宣讲人头。</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>层 A 外滩出海课</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>需求</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>港方课程回迁</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>复旦–港大 EMBA 已办二十七年，港方课长期在复旦教室上，学员对港大归属感弱。年底起港方课迁回外滩中心，需要配得上的到场与体验。</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>场地与体验叙事</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>需求</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>主任先体验</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>潘老师明确：口说不行。先看高质量出海场，主任有兴趣，经管学院层合作才好开展。EMBA 只是其中一小块。</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>层 B 主任体验</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>需求</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>课与孵化可对接</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>本部有企业出海高级管理课，可发资料、谈联合推广。原创谷孵化器、本科研究生海外模块（3–6 个月实习参访）可对接，不塞进本期验收。</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>层 C 备忘不验收</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;L外滩·出海课堂</oddHeader>
     <oddFooter>&amp;R第 &amp;P 页 / 共 &amp;N 页</oddFooter>
     <evenHeader/>
     <evenFooter/>
